--- a/order-no-desig/WarehouseDetail_records(order-no-desig).xlsx
+++ b/order-no-desig/WarehouseDetail_records(order-no-desig).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rndc/Desktop/Work related/Documents/order-no-desig-assign/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rndc/Desktop/Work related/Documents/order-no-desig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDEFD55-87E0-FB47-A740-A5CA0D752D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744EBD89-A137-2B49-AFB6-1E70D6515013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF01000000}"/>
+    <workbookView xWindow="34560" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF01000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(main group)" sheetId="6" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="178">
   <si>
     <t>Current</t>
   </si>
@@ -1594,7 +1594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1622,9 +1622,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2024,7 +2021,9 @@
       <c r="F2" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G2" s="13"/>
+      <c r="G2" t="s">
+        <v>122</v>
+      </c>
       <c r="H2" s="3" t="s">
         <v>172</v>
       </c>
@@ -2058,7 +2057,9 @@
       <c r="F3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="13"/>
+      <c r="G3" t="s">
+        <v>147</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>172</v>
       </c>
@@ -2091,7 +2092,9 @@
       <c r="F4" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" t="s">
+        <v>123</v>
+      </c>
       <c r="H4" s="3" t="s">
         <v>172</v>
       </c>
@@ -2125,7 +2128,9 @@
       <c r="F5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="13"/>
+      <c r="G5" t="s">
+        <v>124</v>
+      </c>
       <c r="H5" s="3" t="s">
         <v>172</v>
       </c>
@@ -2158,7 +2163,9 @@
       <c r="F6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" t="s">
+        <v>148</v>
+      </c>
       <c r="H6" s="3" t="s">
         <v>172</v>
       </c>
@@ -2191,7 +2198,9 @@
       <c r="F7" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" t="s">
+        <v>159</v>
+      </c>
       <c r="H7" s="3" t="s">
         <v>172</v>
       </c>
@@ -2224,7 +2233,9 @@
       <c r="F8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="13"/>
+      <c r="G8" t="s">
+        <v>160</v>
+      </c>
       <c r="H8" s="3" t="s">
         <v>172</v>
       </c>
@@ -2257,7 +2268,9 @@
       <c r="F9" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" t="s">
+        <v>161</v>
+      </c>
       <c r="H9" s="3" t="s">
         <v>172</v>
       </c>
@@ -2290,7 +2303,9 @@
       <c r="F10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G10" s="13"/>
+      <c r="G10" t="s">
+        <v>125</v>
+      </c>
       <c r="H10" s="3" t="s">
         <v>172</v>
       </c>
@@ -2323,7 +2338,9 @@
       <c r="F11" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" t="s">
+        <v>126</v>
+      </c>
       <c r="H11" s="3" t="s">
         <v>172</v>
       </c>
@@ -2356,7 +2373,9 @@
       <c r="F12" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" t="s">
+        <v>127</v>
+      </c>
       <c r="H12" s="3" t="s">
         <v>172</v>
       </c>
@@ -2389,7 +2408,9 @@
       <c r="F13" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" t="s">
+        <v>128</v>
+      </c>
       <c r="H13" s="3" t="s">
         <v>172</v>
       </c>
@@ -2422,7 +2443,9 @@
       <c r="F14" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="13"/>
+      <c r="G14" t="s">
+        <v>129</v>
+      </c>
       <c r="H14" s="3" t="s">
         <v>172</v>
       </c>
@@ -2455,7 +2478,9 @@
       <c r="F15" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" t="s">
+        <v>130</v>
+      </c>
       <c r="H15" s="3" t="s">
         <v>172</v>
       </c>
@@ -2488,7 +2513,9 @@
       <c r="F16" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G16" s="13"/>
+      <c r="G16" t="s">
+        <v>156</v>
+      </c>
       <c r="H16" s="3" t="s">
         <v>172</v>
       </c>
@@ -2521,7 +2548,9 @@
       <c r="F17" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="13"/>
+      <c r="G17" t="s">
+        <v>131</v>
+      </c>
       <c r="H17" s="3" t="s">
         <v>172</v>
       </c>
@@ -2554,7 +2583,9 @@
       <c r="F18" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G18" s="13"/>
+      <c r="G18" t="s">
+        <v>132</v>
+      </c>
       <c r="H18" s="3" t="s">
         <v>172</v>
       </c>
@@ -2587,7 +2618,9 @@
       <c r="F19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G19" s="13"/>
+      <c r="G19" t="s">
+        <v>133</v>
+      </c>
       <c r="H19" s="3" t="s">
         <v>172</v>
       </c>
@@ -2620,7 +2653,9 @@
       <c r="F20" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G20" s="13"/>
+      <c r="G20" t="s">
+        <v>134</v>
+      </c>
       <c r="H20" s="3" t="s">
         <v>172</v>
       </c>
@@ -2653,7 +2688,9 @@
       <c r="F21" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="13"/>
+      <c r="G21" t="s">
+        <v>153</v>
+      </c>
       <c r="H21" s="3" t="s">
         <v>172</v>
       </c>
@@ -2686,7 +2723,9 @@
       <c r="F22" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G22" s="13"/>
+      <c r="G22" t="s">
+        <v>155</v>
+      </c>
       <c r="H22" s="3" t="s">
         <v>172</v>
       </c>
@@ -2719,7 +2758,9 @@
       <c r="F23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G23" s="13"/>
+      <c r="G23" t="s">
+        <v>135</v>
+      </c>
       <c r="H23" s="3" t="s">
         <v>172</v>
       </c>
@@ -2752,7 +2793,9 @@
       <c r="F24" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G24" s="13"/>
+      <c r="G24" t="s">
+        <v>136</v>
+      </c>
       <c r="H24" s="3" t="s">
         <v>172</v>
       </c>
@@ -2785,7 +2828,9 @@
       <c r="F25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G25" s="13"/>
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
       <c r="H25" s="3" t="s">
         <v>172</v>
       </c>
@@ -2818,7 +2863,9 @@
       <c r="F26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="13"/>
+      <c r="G26" t="s">
+        <v>150</v>
+      </c>
       <c r="H26" s="3" t="s">
         <v>172</v>
       </c>
@@ -2851,7 +2898,9 @@
       <c r="F27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G27" s="13"/>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
       <c r="H27" s="3" t="s">
         <v>172</v>
       </c>
@@ -2884,7 +2933,9 @@
       <c r="F28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G28" s="13"/>
+      <c r="G28" t="s">
+        <v>137</v>
+      </c>
       <c r="H28" s="3" t="s">
         <v>172</v>
       </c>
@@ -2917,7 +2968,9 @@
       <c r="F29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G29" s="13"/>
+      <c r="G29" t="s">
+        <v>152</v>
+      </c>
       <c r="H29" s="3" t="s">
         <v>172</v>
       </c>
@@ -2950,7 +3003,9 @@
       <c r="F30" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G30" s="13"/>
+      <c r="G30" t="s">
+        <v>138</v>
+      </c>
       <c r="H30" s="3" t="s">
         <v>172</v>
       </c>
@@ -2983,7 +3038,9 @@
       <c r="F31" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G31" s="13"/>
+      <c r="G31" t="s">
+        <v>139</v>
+      </c>
       <c r="H31" s="3" t="s">
         <v>172</v>
       </c>
@@ -3016,7 +3073,9 @@
       <c r="F32" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G32" s="13"/>
+      <c r="G32" t="s">
+        <v>140</v>
+      </c>
       <c r="H32" s="3" t="s">
         <v>172</v>
       </c>
@@ -3049,7 +3108,9 @@
       <c r="F33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G33" s="13"/>
+      <c r="G33" t="s">
+        <v>141</v>
+      </c>
       <c r="H33" s="3" t="s">
         <v>172</v>
       </c>
@@ -3082,7 +3143,9 @@
       <c r="F34" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="13"/>
+      <c r="G34" t="s">
+        <v>162</v>
+      </c>
       <c r="H34" s="3" t="s">
         <v>172</v>
       </c>
@@ -3115,7 +3178,9 @@
       <c r="F35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G35" s="13"/>
+      <c r="G35" t="s">
+        <v>142</v>
+      </c>
       <c r="H35" s="3" t="s">
         <v>172</v>
       </c>
@@ -3148,7 +3213,9 @@
       <c r="F36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G36" s="12"/>
+      <c r="G36" t="s">
+        <v>121</v>
+      </c>
       <c r="H36" s="3" t="s">
         <v>172</v>
       </c>
@@ -3181,7 +3248,9 @@
       <c r="F37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="13"/>
+      <c r="G37" t="s">
+        <v>157</v>
+      </c>
       <c r="H37" s="3" t="s">
         <v>172</v>
       </c>
@@ -3214,7 +3283,9 @@
       <c r="F38" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G38" s="13"/>
+      <c r="G38" t="s">
+        <v>151</v>
+      </c>
       <c r="H38" s="3" t="s">
         <v>172</v>
       </c>
@@ -3247,7 +3318,9 @@
       <c r="F39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G39" s="13"/>
+      <c r="G39" t="s">
+        <v>143</v>
+      </c>
       <c r="H39" s="3" t="s">
         <v>172</v>
       </c>
@@ -3280,7 +3353,9 @@
       <c r="F40" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="13"/>
+      <c r="G40" t="s">
+        <v>144</v>
+      </c>
       <c r="H40" s="3" t="s">
         <v>172</v>
       </c>
@@ -3313,7 +3388,9 @@
       <c r="F41" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G41" s="13"/>
+      <c r="G41" t="s">
+        <v>145</v>
+      </c>
       <c r="H41" s="3" t="s">
         <v>172</v>
       </c>
@@ -3346,7 +3423,9 @@
       <c r="F42" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G42" s="13"/>
+      <c r="G42" t="s">
+        <v>163</v>
+      </c>
       <c r="H42" s="3" t="s">
         <v>172</v>
       </c>
@@ -3379,7 +3458,9 @@
       <c r="F43" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G43" s="13"/>
+      <c r="G43" t="s">
+        <v>158</v>
+      </c>
       <c r="H43" s="3" t="s">
         <v>172</v>
       </c>
@@ -3412,7 +3493,9 @@
       <c r="F44" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G44" s="13"/>
+      <c r="G44" t="s">
+        <v>146</v>
+      </c>
       <c r="H44" s="3" t="s">
         <v>172</v>
       </c>
@@ -3433,7 +3516,7 @@
       <c r="D51" s="11"/>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C52" s="14">
+      <c r="C52" s="13">
         <v>1</v>
       </c>
       <c r="D52" s="11" t="s">
@@ -3441,7 +3524,7 @@
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C53" s="14">
+      <c r="C53" s="13">
         <v>40</v>
       </c>
       <c r="D53" s="11" t="s">
